--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.8795</v>
+        <v>17.09404</v>
       </c>
       <c r="D2" t="n">
-        <v>16.78929</v>
+        <v>16.70453</v>
       </c>
       <c r="E2" t="n">
-        <v>16.86141</v>
+        <v>16.73754</v>
       </c>
       <c r="F2" t="n">
-        <v>43.6435</v>
+        <v>43.93486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05016</v>
+        <v>0.05136</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83594</v>
+        <v>1.79491</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.23215</v>
+        <v>16.98832</v>
       </c>
       <c r="D3" t="n">
-        <v>17.04052</v>
+        <v>16.55895</v>
       </c>
       <c r="E3" t="n">
-        <v>17.28245</v>
+        <v>16.97239</v>
       </c>
       <c r="F3" t="n">
-        <v>42.77573</v>
+        <v>42.93246</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05014</v>
+        <v>0.05142</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86533</v>
+        <v>1.82223</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.05201</v>
+        <v>16.83207</v>
       </c>
       <c r="D4" t="n">
-        <v>17.09309</v>
+        <v>16.77762</v>
       </c>
       <c r="E4" t="n">
-        <v>16.71915</v>
+        <v>16.83123</v>
       </c>
       <c r="F4" t="n">
-        <v>43.77501</v>
+        <v>42.53294</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05192</v>
+        <v>0.05175</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87966</v>
+        <v>1.85538</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.66646</v>
+        <v>16.88288</v>
       </c>
       <c r="D6" t="n">
-        <v>16.33853</v>
+        <v>16.21752</v>
       </c>
       <c r="E6" t="n">
-        <v>16.52582</v>
+        <v>16.75621</v>
       </c>
       <c r="F6" t="n">
-        <v>21.85586</v>
+        <v>21.99519</v>
       </c>
       <c r="G6" t="n">
-        <v>33.61606</v>
+        <v>34.34184</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.98493</v>
+        <v>16.98278</v>
       </c>
       <c r="D7" t="n">
-        <v>16.01071</v>
+        <v>16.31396</v>
       </c>
       <c r="E7" t="n">
-        <v>16.49377</v>
+        <v>16.70243</v>
       </c>
       <c r="F7" t="n">
-        <v>22.43494</v>
+        <v>21.98677</v>
       </c>
       <c r="G7" t="n">
-        <v>34.328</v>
+        <v>34.68161</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.00199</v>
+        <v>17.31974</v>
       </c>
       <c r="D8" t="n">
-        <v>16.03972</v>
+        <v>16.17871</v>
       </c>
       <c r="E8" t="n">
-        <v>16.54163</v>
+        <v>16.6091</v>
       </c>
       <c r="F8" t="n">
-        <v>22.1668</v>
+        <v>21.65947</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58797</v>
+        <v>34.29584</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61886</v>
+        <v>0.61383</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12116</v>
+        <v>1.12412</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60701</v>
+        <v>0.6224499999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>1.14792</v>
+        <v>1.11852</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61654</v>
+        <v>0.61424</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13675</v>
+        <v>1.12409</v>
       </c>
     </row>
   </sheetData>
